--- a/雅思听力/听力复盘分析表.xlsx
+++ b/雅思听力/听力复盘分析表.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1294" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="275">
   <si>
     <t>雅思听力 填空题「七坑」深度分析表（Section 1 &amp; 4）</t>
   </si>
@@ -340,6 +340,13 @@
     <t>Q7</t>
   </si>
   <si>
+    <t>So if I 
+book your Shuttle for after 12.00 -let's say, 12.30: that should give 
+you plenty of time to, you know, collect your baggage, maybe grab a 
+coffee? 
+Yeah, that</t>
+  </si>
+  <si>
     <r>
       <t>passengers: One=</t>
     </r>
@@ -363,13 +370,149 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve"> you said your expected time</t>
+  </si>
+  <si>
+    <t>your expected time=》so=&gt;So if I 
+book your Shuttle for after 12.00 -let's say, 12.30: that should give 
+you plenty of time to, you know, collect your baggage, maybe grab a 
+coffee? 
+Yeah, that</t>
+  </si>
+  <si>
     <t>Q8</t>
   </si>
   <si>
+    <t>Thomson</t>
+  </si>
+  <si>
+    <t>No, it's T-H-0-M-S-0-N.</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>And what's your name, please?</t>
+  </si>
+  <si>
+    <r>
+      <t>And what's your name, please?=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E293B"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>》</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E293B"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>no=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E293B"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>》</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E293B"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>No, it's T-H-0-M-S-0-N.</t>
+    </r>
+  </si>
+  <si>
     <t>Q9</t>
   </si>
   <si>
+    <t>AC936</t>
+  </si>
+  <si>
+    <t>Oh, it's Air Canada flight number AC936,</t>
+  </si>
+  <si>
+    <t>flight number</t>
+  </si>
+  <si>
+    <r>
+      <t>flight number=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E293B"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>》</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E293B"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Oh, it's Air Canada flight number AC936,</t>
+    </r>
+  </si>
+  <si>
     <t>Q10</t>
+  </si>
+  <si>
+    <t>330384502045607</t>
+  </si>
+  <si>
+    <t>3303845020456837</t>
+  </si>
+  <si>
+    <t>错</t>
+  </si>
+  <si>
+    <t>Yes, it's a VISA card, and the number is 3303 8450 2045 6837.</t>
+  </si>
+  <si>
+    <t>it's a VISA card, a</t>
+  </si>
+  <si>
+    <r>
+      <t>it's a VISA card, =</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E293B"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>》</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E293B"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3303 8450 2045 6837.</t>
+    </r>
+  </si>
+  <si>
+    <t>最后几位数字听不清，专门训练数字听写</t>
   </si>
   <si>
     <t>📝 Section 4（题目 Q31–Q40）</t>
@@ -964,7 +1107,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1024,6 +1167,18 @@
       <sz val="10"/>
       <color rgb="FF1E293B"/>
       <name val="宋体-简"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.1"/>
+      <color rgb="FF141414"/>
+      <name val="Times-Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF141414"/>
+      <name val="Times-Roman"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1592,28 +1747,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1622,122 +1768,131 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1850,6 +2005,13 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1860,6 +2022,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2222,7 +2387,7 @@
     <col min="10" max="10" width="18" customWidth="1"/>
     <col min="11" max="11" width="12" customWidth="1"/>
     <col min="12" max="12" width="15.5769230769231" customWidth="1"/>
-    <col min="13" max="13" width="30" customWidth="1"/>
+    <col min="13" max="13" width="29.8076923076923" customWidth="1"/>
     <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="20" customWidth="1"/>
     <col min="16" max="16" width="6" customWidth="1"/>
@@ -2580,18 +2745,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" ht="52" customHeight="1" spans="1:16">
+    <row r="11" ht="152" spans="1:16">
       <c r="A11" s="14" t="s">
         <v>62</v>
       </c>
       <c r="B11" s="34">
-        <v>0.5</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>2</v>
+        <v>0.520833333333333</v>
+      </c>
+      <c r="C11" s="34">
+        <v>0.520833333333333</v>
+      </c>
+      <c r="D11" s="31" t="s">
+        <v>57</v>
       </c>
       <c r="E11" s="32" t="s">
         <v>2</v>
@@ -2600,13 +2765,13 @@
         <v>2</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="I11" s="37" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J11" s="32" t="s">
         <v>2</v>
@@ -2615,10 +2780,10 @@
         <v>2</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="M11" s="5" t="s">
-        <v>2</v>
+        <v>65</v>
+      </c>
+      <c r="M11" s="38" t="s">
+        <v>66</v>
       </c>
       <c r="N11" s="5" t="s">
         <v>2</v>
@@ -2632,16 +2797,16 @@
     </row>
     <row r="12" ht="52" customHeight="1" spans="1:16">
       <c r="A12" s="15" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>2</v>
+        <v>68</v>
+      </c>
+      <c r="D12" s="31" t="s">
+        <v>57</v>
       </c>
       <c r="E12" s="32" t="s">
         <v>2</v>
@@ -2650,13 +2815,13 @@
         <v>2</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="J12" s="32" t="s">
         <v>2</v>
@@ -2665,10 +2830,10 @@
         <v>2</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="M12" s="4" t="s">
-        <v>2</v>
+        <v>71</v>
+      </c>
+      <c r="M12" s="36" t="s">
+        <v>72</v>
       </c>
       <c r="N12" s="4" t="s">
         <v>2</v>
@@ -2682,16 +2847,16 @@
     </row>
     <row r="13" ht="52" customHeight="1" spans="1:16">
       <c r="A13" s="14" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>2</v>
+        <v>74</v>
+      </c>
+      <c r="D13" s="31" t="s">
+        <v>57</v>
       </c>
       <c r="E13" s="32" t="s">
         <v>2</v>
@@ -2700,7 +2865,7 @@
         <v>2</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>2</v>
@@ -2715,10 +2880,10 @@
         <v>2</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="M13" s="5" t="s">
-        <v>2</v>
+        <v>76</v>
+      </c>
+      <c r="M13" s="37" t="s">
+        <v>77</v>
       </c>
       <c r="N13" s="5" t="s">
         <v>2</v>
@@ -2732,16 +2897,16 @@
     </row>
     <row r="14" ht="52" customHeight="1" spans="1:16">
       <c r="A14" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>2</v>
+        <v>78</v>
+      </c>
+      <c r="B14" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" s="31" t="s">
+        <v>81</v>
       </c>
       <c r="E14" s="32" t="s">
         <v>2</v>
@@ -2749,8 +2914,8 @@
       <c r="F14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G14" s="4" t="s">
-        <v>2</v>
+      <c r="G14" s="39" t="s">
+        <v>82</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>2</v>
@@ -2765,16 +2930,16 @@
         <v>2</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="M14" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="N14" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="O14" s="4" t="s">
-        <v>2</v>
+        <v>83</v>
+      </c>
+      <c r="M14" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="N14" s="4">
+        <v>1</v>
+      </c>
+      <c r="O14" s="40" t="s">
+        <v>85</v>
       </c>
       <c r="P14" s="17" t="s">
         <v>2</v>
@@ -2782,7 +2947,7 @@
     </row>
     <row r="16" ht="26" customHeight="1" spans="1:16">
       <c r="A16" s="28" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1" spans="1:16">
@@ -2796,7 +2961,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="E17" s="30" t="s">
         <v>11</v>
@@ -2837,7 +3002,7 @@
     </row>
     <row r="18" ht="52" customHeight="1" spans="1:16">
       <c r="A18" s="14" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>2</v>
@@ -2887,7 +3052,7 @@
     </row>
     <row r="19" ht="52" customHeight="1" spans="1:16">
       <c r="A19" s="15" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>2</v>
@@ -2937,7 +3102,7 @@
     </row>
     <row r="20" ht="52" customHeight="1" spans="1:16">
       <c r="A20" s="14" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>2</v>
@@ -2987,7 +3152,7 @@
     </row>
     <row r="21" ht="52" customHeight="1" spans="1:16">
       <c r="A21" s="15" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>2</v>
@@ -3037,7 +3202,7 @@
     </row>
     <row r="22" ht="52" customHeight="1" spans="1:16">
       <c r="A22" s="14" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>2</v>
@@ -3087,7 +3252,7 @@
     </row>
     <row r="23" ht="52" customHeight="1" spans="1:16">
       <c r="A23" s="15" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>2</v>
@@ -3137,7 +3302,7 @@
     </row>
     <row r="24" ht="52" customHeight="1" spans="1:16">
       <c r="A24" s="14" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>2</v>
@@ -3187,7 +3352,7 @@
     </row>
     <row r="25" ht="52" customHeight="1" spans="1:16">
       <c r="A25" s="15" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>2</v>
@@ -3237,7 +3402,7 @@
     </row>
     <row r="26" ht="52" customHeight="1" spans="1:16">
       <c r="A26" s="14" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>2</v>
@@ -3287,7 +3452,7 @@
     </row>
     <row r="27" ht="52" customHeight="1" spans="1:16">
       <c r="A27" s="15" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>2</v>
@@ -3337,84 +3502,84 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:16">
       <c r="A28" s="20" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" ht="31" spans="1:16">
-      <c r="A29" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="B29" s="39" t="s">
-        <v>81</v>
-      </c>
-      <c r="H29" s="39" t="s">
-        <v>82</v>
+      <c r="A29" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="B29" s="42" t="s">
+        <v>100</v>
+      </c>
+      <c r="H29" s="42" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:16">
-      <c r="A30" s="40" t="s">
-        <v>83</v>
-      </c>
-      <c r="B30" s="41" t="s">
-        <v>84</v>
-      </c>
-      <c r="H30" s="41" t="s">
-        <v>85</v>
+      <c r="A30" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="B30" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="H30" s="44" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1" spans="1:16">
-      <c r="A31" s="38" t="s">
-        <v>86</v>
-      </c>
-      <c r="B31" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="H31" s="39" t="s">
-        <v>88</v>
+      <c r="A31" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="B31" s="42" t="s">
+        <v>106</v>
+      </c>
+      <c r="H31" s="42" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1" spans="1:16">
-      <c r="A32" s="40" t="s">
-        <v>89</v>
-      </c>
-      <c r="B32" s="41" t="s">
-        <v>90</v>
-      </c>
-      <c r="H32" s="41" t="s">
-        <v>91</v>
+      <c r="A32" s="43" t="s">
+        <v>108</v>
+      </c>
+      <c r="B32" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="H32" s="44" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1" spans="1:8">
-      <c r="A33" s="38" t="s">
-        <v>92</v>
-      </c>
-      <c r="B33" s="39" t="s">
-        <v>93</v>
-      </c>
-      <c r="H33" s="39" t="s">
-        <v>94</v>
+      <c r="A33" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="B33" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="H33" s="42" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1" spans="1:8">
-      <c r="A34" s="40" t="s">
-        <v>95</v>
-      </c>
-      <c r="B34" s="41" t="s">
-        <v>96</v>
-      </c>
-      <c r="H34" s="41" t="s">
-        <v>97</v>
+      <c r="A34" s="43" t="s">
+        <v>114</v>
+      </c>
+      <c r="B34" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="H34" s="44" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1" spans="1:8">
-      <c r="A35" s="38" t="s">
-        <v>98</v>
-      </c>
-      <c r="B35" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="H35" s="39" t="s">
-        <v>100</v>
+      <c r="A35" s="41" t="s">
+        <v>117</v>
+      </c>
+      <c r="B35" s="42" t="s">
+        <v>118</v>
+      </c>
+      <c r="H35" s="42" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -3470,7 +3635,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:14">
@@ -3487,15 +3652,15 @@
         <v>2</v>
       </c>
       <c r="K2" s="23" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:14">
       <c r="A3" s="24" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:14">
@@ -3503,7 +3668,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>8</v>
@@ -3512,39 +3677,39 @@
         <v>9</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="G4" s="18" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="M4" s="18" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1" spans="1:14">
       <c r="A5" s="14" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>2</v>
@@ -3588,7 +3753,7 @@
     </row>
     <row r="6" ht="58" customHeight="1" spans="1:14">
       <c r="A6" s="15" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>2</v>
@@ -3632,7 +3797,7 @@
     </row>
     <row r="7" ht="58" customHeight="1" spans="1:14">
       <c r="A7" s="14" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>2</v>
@@ -3676,7 +3841,7 @@
     </row>
     <row r="8" ht="58" customHeight="1" spans="1:14">
       <c r="A8" s="15" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>2</v>
@@ -3720,7 +3885,7 @@
     </row>
     <row r="9" ht="58" customHeight="1" spans="1:14">
       <c r="A9" s="14" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>2</v>
@@ -3764,7 +3929,7 @@
     </row>
     <row r="10" ht="58" customHeight="1" spans="1:14">
       <c r="A10" s="15" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>2</v>
@@ -3808,7 +3973,7 @@
     </row>
     <row r="11" ht="58" customHeight="1" spans="1:14">
       <c r="A11" s="14" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>2</v>
@@ -3852,7 +4017,7 @@
     </row>
     <row r="12" ht="58" customHeight="1" spans="1:14">
       <c r="A12" s="15" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>2</v>
@@ -3896,7 +4061,7 @@
     </row>
     <row r="13" ht="58" customHeight="1" spans="1:14">
       <c r="A13" s="14" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>2</v>
@@ -3940,7 +4105,7 @@
     </row>
     <row r="14" ht="58" customHeight="1" spans="1:14">
       <c r="A14" s="15" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>2</v>
@@ -3984,7 +4149,7 @@
     </row>
     <row r="16" ht="26" customHeight="1" spans="1:14">
       <c r="A16" s="24" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:14">
@@ -3992,7 +4157,7 @@
         <v>7</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>8</v>
@@ -4001,39 +4166,39 @@
         <v>9</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="M17" s="18" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1" spans="1:14">
       <c r="A18" s="14" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>2</v>
@@ -4077,7 +4242,7 @@
     </row>
     <row r="19" ht="58" customHeight="1" spans="1:14">
       <c r="A19" s="15" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>2</v>
@@ -4121,7 +4286,7 @@
     </row>
     <row r="20" ht="58" customHeight="1" spans="1:14">
       <c r="A20" s="14" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>2</v>
@@ -4165,7 +4330,7 @@
     </row>
     <row r="21" ht="58" customHeight="1" spans="1:14">
       <c r="A21" s="15" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>2</v>
@@ -4209,7 +4374,7 @@
     </row>
     <row r="22" ht="58" customHeight="1" spans="1:14">
       <c r="A22" s="14" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>2</v>
@@ -4253,7 +4418,7 @@
     </row>
     <row r="23" ht="58" customHeight="1" spans="1:14">
       <c r="A23" s="15" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>2</v>
@@ -4297,7 +4462,7 @@
     </row>
     <row r="24" ht="58" customHeight="1" spans="1:14">
       <c r="A24" s="14" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>2</v>
@@ -4341,7 +4506,7 @@
     </row>
     <row r="25" ht="58" customHeight="1" spans="1:14">
       <c r="A25" s="15" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>2</v>
@@ -4385,7 +4550,7 @@
     </row>
     <row r="26" ht="58" customHeight="1" spans="1:14">
       <c r="A26" s="14" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>2</v>
@@ -4429,7 +4594,7 @@
     </row>
     <row r="27" ht="58" customHeight="1" spans="1:14">
       <c r="A27" s="15" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>2</v>
@@ -4473,106 +4638,106 @@
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:14">
       <c r="A29" s="20" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:14">
       <c r="A30" s="25" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="H30" s="19" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1" spans="1:14">
       <c r="A31" s="26" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="H31" s="27" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1" spans="1:14">
       <c r="A32" s="25" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="H32" s="19" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1" spans="1:8">
       <c r="A33" s="26" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="H33" s="27" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1" spans="1:8">
       <c r="A34" s="25" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="H34" s="19" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1" spans="1:8">
       <c r="A35" s="26" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="H35" s="27" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1" spans="1:8">
       <c r="A36" s="25" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="H36" s="19" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1" spans="1:8">
       <c r="A37" s="26" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="H37" s="27" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1" spans="1:8">
       <c r="A38" s="25" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="H38" s="19" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -4630,34 +4795,34 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:11">
       <c r="A2" s="16" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:11">
       <c r="A3" s="17" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="H3" s="17" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:11">
       <c r="A4" s="16" t="s">
-        <v>171</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" ht="48" customHeight="1" spans="1:11">
@@ -4665,7 +4830,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>8</v>
@@ -4674,25 +4839,25 @@
         <v>9</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="G5" s="18" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="H5" s="18" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="I5" s="18" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1" spans="1:11">
@@ -4942,7 +5107,7 @@
     </row>
     <row r="13" ht="60" customHeight="1" spans="1:11">
       <c r="A13" s="15" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>2</v>
@@ -4977,95 +5142,95 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:11">
       <c r="A15" s="20" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:11">
       <c r="A16" s="21" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:8">
       <c r="A17" s="22" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="H17" s="17" t="s">
-        <v>184</v>
+        <v>203</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:8">
       <c r="A18" s="21" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:8">
       <c r="A19" s="22" t="s">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:8">
       <c r="A20" s="21" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:8">
       <c r="A21" s="22" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="H21" s="17" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:8">
       <c r="A22" s="21" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:8">
       <c r="A23" s="22" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="H23" s="17" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -5115,44 +5280,44 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>204</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:10">
       <c r="A3" s="3" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:10">
@@ -5413,39 +5578,39 @@
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:10">
       <c r="A13" s="6" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:10">
       <c r="A14" s="7" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:10">
@@ -5706,39 +5871,39 @@
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:10">
       <c r="A24" s="8" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1" spans="1:10">
       <c r="A25" s="9" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:10">
@@ -5999,39 +6164,39 @@
     </row>
     <row r="35" ht="30" customHeight="1" spans="1:10">
       <c r="A35" s="10" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1" spans="1:10">
       <c r="A36" s="11" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="D36" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="G36" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="H36" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="I36" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="J36" s="11" t="s">
         <v>233</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="F36" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="G36" s="11" t="s">
-        <v>235</v>
-      </c>
-      <c r="H36" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="I36" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="J36" s="11" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="37" ht="24" customHeight="1" spans="1:10">
@@ -6292,44 +6457,44 @@
     </row>
     <row r="46" ht="30" customHeight="1" spans="1:10">
       <c r="A46" s="12" t="s">
-        <v>238</v>
+        <v>257</v>
       </c>
     </row>
     <row r="47" ht="32" customHeight="1" spans="1:10">
       <c r="A47" s="13" t="s">
-        <v>239</v>
+        <v>258</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>243</v>
+        <v>262</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>244</v>
+        <v>263</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="I47" s="13" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="J47" s="13" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
     </row>
     <row r="48" ht="28" customHeight="1" spans="1:10">
       <c r="A48" s="14" t="s">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>2</v>
@@ -6361,7 +6526,7 @@
     </row>
     <row r="49" ht="28" customHeight="1" spans="1:10">
       <c r="A49" s="15" t="s">
-        <v>249</v>
+        <v>268</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>2</v>
@@ -6393,7 +6558,7 @@
     </row>
     <row r="50" ht="28" customHeight="1" spans="1:10">
       <c r="A50" s="14" t="s">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>2</v>
@@ -6425,7 +6590,7 @@
     </row>
     <row r="51" ht="28" customHeight="1" spans="1:10">
       <c r="A51" s="15" t="s">
-        <v>251</v>
+        <v>270</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>2</v>
@@ -6457,7 +6622,7 @@
     </row>
     <row r="52" ht="28" customHeight="1" spans="1:10">
       <c r="A52" s="14" t="s">
-        <v>252</v>
+        <v>271</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>2</v>
@@ -6489,7 +6654,7 @@
     </row>
     <row r="53" ht="28" customHeight="1" spans="1:10">
       <c r="A53" s="15" t="s">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>2</v>
@@ -6521,7 +6686,7 @@
     </row>
     <row r="54" ht="28" customHeight="1" spans="1:10">
       <c r="A54" s="14" t="s">
-        <v>254</v>
+        <v>273</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>2</v>
@@ -6553,7 +6718,7 @@
     </row>
     <row r="55" ht="28" customHeight="1" spans="1:10">
       <c r="A55" s="15" t="s">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>2</v>
